--- a/data/trans_dic/IP16A05-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 16,06</t>
+          <t>1,77; 16,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,01; 29,55</t>
+          <t>9,2; 29,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,01; 33,73</t>
+          <t>9,27; 33,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,87; 40,83</t>
+          <t>7,85; 40,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 26,18</t>
+          <t>4,51; 24,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 24,25</t>
+          <t>5,82; 24,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 34,49</t>
+          <t>8,19; 37,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,05</t>
+          <t>0,0; 9,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 16,37</t>
+          <t>4,35; 16,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 23,01</t>
+          <t>9,4; 23,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,1; 29,99</t>
+          <t>11,85; 29,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 19,21</t>
+          <t>4,04; 19,4</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 24,28</t>
+          <t>7,6; 24,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,43; 30,61</t>
+          <t>10,88; 29,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,46; 26,93</t>
+          <t>7,24; 25,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 34,94</t>
+          <t>7,22; 35,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 22,72</t>
+          <t>7,51; 22,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 25,05</t>
+          <t>9,68; 25,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 24,43</t>
+          <t>5,67; 21,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 21,92</t>
+          <t>5,52; 20,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 21,08</t>
+          <t>9,05; 20,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,37; 24,56</t>
+          <t>12,42; 24,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,07; 19,53</t>
+          <t>8,51; 20,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 23,04</t>
+          <t>7,83; 23,66</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,65</t>
+          <t>0,0; 20,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 29,89</t>
+          <t>7,13; 30,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 13,2</t>
+          <t>1,51; 13,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 18,3</t>
+          <t>3,12; 18,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 23,69</t>
+          <t>2,83; 25,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 27,06</t>
+          <t>4,0; 28,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 26,39</t>
+          <t>6,42; 28,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 17,3</t>
+          <t>1,91; 18,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 18,71</t>
+          <t>4,08; 17,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 23,98</t>
+          <t>7,89; 24,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 15,89</t>
+          <t>4,51; 16,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 13,7</t>
+          <t>3,4; 14,4</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 19,23</t>
+          <t>1,93; 17,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 30,54</t>
+          <t>5,86; 30,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,23</t>
+          <t>0,0; 21,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>0,0; 5,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,48</t>
+          <t>0,0; 10,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,04</t>
+          <t>0,0; 15,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,22</t>
+          <t>0,0; 20,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,7</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,6</t>
+          <t>1,8; 10,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 19,72</t>
+          <t>5,05; 19,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 16,84</t>
+          <t>1,73; 16,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,73</t>
+          <t>0,32; 3,66</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 13,73</t>
+          <t>5,14; 13,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,88; 23,92</t>
+          <t>12,83; 23,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 16,59</t>
+          <t>7,72; 16,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 14,54</t>
+          <t>4,53; 14,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 15,09</t>
+          <t>6,8; 14,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,82; 18,12</t>
+          <t>8,86; 17,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,73; 18,77</t>
+          <t>8,27; 18,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,11</t>
+          <t>3,17; 9,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,83; 12,52</t>
+          <t>6,87; 12,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 19,17</t>
+          <t>12,25; 19,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,44; 16,06</t>
+          <t>9,47; 16,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 10,42</t>
+          <t>4,72; 9,94</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1756</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6520</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5359</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4865</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4616</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11385</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9974</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3754</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>513; 4800</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3359; 10866</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2507; 8998</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1255; 6455</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1339; 7290</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2237; 9585</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1963; 8930</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2123</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2556; 9728</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7040; 17312</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6045; 14940</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1550; 7438</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6118</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10538</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6217</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7263</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7127</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11055</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5367</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5749</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>13245</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21593</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>11585</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>13012</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3284; 10771</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5891; 16192</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3059; 10629</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3365; 16405</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3826; 11522</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6460; 16853</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2443; 9425</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2706; 10194</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>8526; 19489</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>15020; 29684</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>7259; 17171</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>7490; 22623</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5039</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3152</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2751</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4561</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4047</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8308</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6306</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>6156</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4545</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2130; 8973</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>545; 4812</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1159; 6942</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>675; 6132</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1115; 8064</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2147; 9695</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>880; 8397</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1894; 8200</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4562; 14069</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3137; 11243</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2830; 11999</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4278</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1574</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3257</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5553</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1890</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>590; 5370</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1593; 8348</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4747</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4660</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4317</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3876</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4702</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3169</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1262; 7271</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2627; 10066</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>774; 7547</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>457; 5220</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>11155</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26375</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14895</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15013</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20465</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>16058</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9798</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>25837</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>46840</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>30953</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>24812</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>6445; 17141</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>18949; 34234</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9846; 21561</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8044; 25937</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9792; 21384</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13999; 28216</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10193; 23328</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5777; 17076</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>18490; 34483</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>37430; 58313</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>23748; 40852</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>16992; 35777</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A05-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 16,53</t>
+          <t>1,79; 15,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 29,77</t>
+          <t>9,98; 30,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,27; 33,29</t>
+          <t>10,1; 35,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,85; 40,39</t>
+          <t>8,2; 39,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 24,58</t>
+          <t>4,38; 25,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 24,94</t>
+          <t>5,15; 23,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,19; 37,24</t>
+          <t>8,62; 35,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,5</t>
+          <t>0,0; 12,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 16,58</t>
+          <t>4,07; 16,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,4; 23,11</t>
+          <t>8,97; 22,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,85; 29,29</t>
+          <t>12,18; 29,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 19,4</t>
+          <t>3,95; 20,65</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,6; 24,92</t>
+          <t>6,51; 24,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,88; 29,89</t>
+          <t>11,72; 30,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 25,16</t>
+          <t>7,3; 24,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,22; 35,19</t>
+          <t>6,79; 34,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 22,61</t>
+          <t>7,39; 23,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,68; 25,25</t>
+          <t>9,57; 25,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 21,87</t>
+          <t>6,14; 24,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 20,81</t>
+          <t>5,5; 21,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 20,69</t>
+          <t>9,05; 20,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,42; 24,55</t>
+          <t>12,42; 24,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 20,12</t>
+          <t>8,6; 20,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,83; 23,66</t>
+          <t>8,41; 23,54</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,19</t>
+          <t>0,0; 17,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 30,04</t>
+          <t>7,59; 32,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,32</t>
+          <t>1,53; 13,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 18,69</t>
+          <t>3,03; 18,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 25,69</t>
+          <t>2,91; 26,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 28,89</t>
+          <t>3,07; 25,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 28,99</t>
+          <t>5,13; 26,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 18,19</t>
+          <t>1,82; 17,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 17,68</t>
+          <t>3,05; 16,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,89; 24,35</t>
+          <t>7,81; 24,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 16,16</t>
+          <t>4,6; 15,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 14,4</t>
+          <t>3,38; 14,1</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 17,58</t>
+          <t>2,0; 16,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 30,73</t>
+          <t>7,25; 30,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,51</t>
+          <t>0,0; 21,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,98</t>
+          <t>0,0; 6,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,95</t>
+          <t>0,0; 10,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,59</t>
+          <t>0,0; 18,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,66</t>
+          <t>0,0; 22,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 5,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 10,39</t>
+          <t>1,78; 10,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 19,34</t>
+          <t>5,25; 19,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 16,84</t>
+          <t>1,71; 15,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,66</t>
+          <t>0,36; 3,91</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 13,68</t>
+          <t>5,27; 13,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,83; 23,18</t>
+          <t>12,97; 23,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 16,92</t>
+          <t>7,5; 16,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 14,59</t>
+          <t>4,49; 14,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 14,86</t>
+          <t>6,59; 14,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 17,86</t>
+          <t>9,09; 18,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,27; 18,92</t>
+          <t>8,47; 19,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,17; 9,37</t>
+          <t>2,99; 9,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 12,81</t>
+          <t>6,53; 12,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 19,08</t>
+          <t>12,03; 19,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,47; 16,29</t>
+          <t>9,13; 16,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 9,94</t>
+          <t>4,51; 10,02</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>513; 4800</t>
+          <t>520; 4633</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3359; 10866</t>
+          <t>3642; 11178</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2507; 8998</t>
+          <t>2731; 9599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1255; 6455</t>
+          <t>1311; 6280</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1339; 7290</t>
+          <t>1299; 7635</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2237; 9585</t>
+          <t>1980; 8999</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1963; 8930</t>
+          <t>2066; 8618</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2123</t>
+          <t>0; 2701</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2556; 9728</t>
+          <t>2390; 9478</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7040; 17312</t>
+          <t>6721; 16673</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6045; 14940</t>
+          <t>6214; 15128</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1550; 7438</t>
+          <t>1513; 7917</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3284; 10771</t>
+          <t>2813; 10531</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5891; 16192</t>
+          <t>6349; 16489</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3059; 10629</t>
+          <t>3082; 10527</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3365; 16405</t>
+          <t>3165; 15924</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3826; 11522</t>
+          <t>3765; 11775</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6460; 16853</t>
+          <t>6392; 17100</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2443; 9425</t>
+          <t>2645; 10413</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2706; 10194</t>
+          <t>2695; 10728</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8526; 19489</t>
+          <t>8520; 19278</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15020; 29684</t>
+          <t>15019; 29636</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7259; 17171</t>
+          <t>7338; 17779</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7490; 22623</t>
+          <t>8038; 22509</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4545</t>
+          <t>0; 3931</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2130; 8973</t>
+          <t>2266; 9738</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>545; 4812</t>
+          <t>551; 4779</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1159; 6942</t>
+          <t>1127; 7040</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>675; 6132</t>
+          <t>694; 6264</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1115; 8064</t>
+          <t>858; 7143</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2147; 9695</t>
+          <t>1715; 8995</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>880; 8397</t>
+          <t>841; 8152</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1894; 8200</t>
+          <t>1413; 7794</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4562; 14069</t>
+          <t>4515; 13942</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3137; 11243</t>
+          <t>3202; 10964</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2830; 11999</t>
+          <t>2813; 11746</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>590; 5370</t>
+          <t>612; 5146</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1593; 8348</t>
+          <t>1971; 8245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4747</t>
+          <t>0; 4778</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4660</t>
+          <t>0; 4796</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4317</t>
+          <t>0; 4275</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3876</t>
+          <t>0; 4516</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4702</t>
+          <t>0; 5120</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3169</t>
+          <t>0; 3572</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1262; 7271</t>
+          <t>1249; 7185</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2627; 10066</t>
+          <t>2731; 10116</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>774; 7547</t>
+          <t>765; 7066</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>457; 5220</t>
+          <t>510; 5578</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6445; 17141</t>
+          <t>6600; 17356</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18949; 34234</t>
+          <t>19150; 34373</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9846; 21561</t>
+          <t>9561; 20678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8044; 25937</t>
+          <t>7984; 25286</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9792; 21384</t>
+          <t>9481; 20949</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13999; 28216</t>
+          <t>14362; 29524</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10193; 23328</t>
+          <t>10447; 23916</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5777; 17076</t>
+          <t>5454; 16563</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18490; 34483</t>
+          <t>17591; 34355</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37430; 58313</t>
+          <t>36772; 58807</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23748; 40852</t>
+          <t>22883; 40249</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16992; 35777</t>
+          <t>16231; 36075</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A05-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,66%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19,25%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6,05%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>17,86%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>19,82%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,25%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 15,96</t>
+          <t>4,43; 26,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 30,63</t>
+          <t>5,06; 24,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,1; 35,51</t>
+          <t>8,42; 34,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,2; 39,29</t>
+          <t>0,0; 13,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 25,74</t>
+          <t>1,75; 16,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 23,42</t>
+          <t>9,01; 29,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,62; 35,94</t>
+          <t>10,01; 33,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,08</t>
+          <t>8,35; 42,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 16,15</t>
+          <t>4,4; 16,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,97; 22,25</t>
+          <t>9,23; 23,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,18; 29,66</t>
+          <t>12,1; 29,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 20,65</t>
+          <t>4,3; 21,79</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16,56%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>14,16%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>19,46%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>14,72%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>16,56%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 24,36</t>
+          <t>7,46; 22,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 30,44</t>
+          <t>9,62; 25,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 24,92</t>
+          <t>6,03; 24,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,79; 34,16</t>
+          <t>5,66; 22,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,39; 23,11</t>
+          <t>7,45; 24,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,57; 25,62</t>
+          <t>11,43; 30,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 24,16</t>
+          <t>8,46; 26,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 21,9</t>
+          <t>4,89; 18,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 20,47</t>
+          <t>8,84; 21,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,42; 24,51</t>
+          <t>12,37; 24,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 20,83</t>
+          <t>8,07; 19,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 23,54</t>
+          <t>6,83; 17,87</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,53%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13,64%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16,87%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,83%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,64%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,47</t>
+          <t>2,88; 23,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,59; 32,6</t>
+          <t>3,04; 27,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 13,23</t>
+          <t>6,33; 26,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 18,95</t>
+          <t>1,97; 17,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 26,25</t>
+          <t>0,0; 17,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 25,59</t>
+          <t>6,98; 29,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 26,89</t>
+          <t>1,52; 13,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 17,66</t>
+          <t>3,14; 18,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 16,81</t>
+          <t>3,07; 18,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,81; 24,13</t>
+          <t>7,77; 23,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 15,76</t>
+          <t>4,28; 15,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 14,1</t>
+          <t>3,22; 14,22</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,5%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15,75%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7,13%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 16,85</t>
+          <t>0,0; 11,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 30,35</t>
+          <t>0,0; 16,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,65</t>
+          <t>0,0; 20,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,15</t>
+          <t>0,0; 6,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,84</t>
+          <t>1,99; 19,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,16</t>
+          <t>7,32; 30,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,5</t>
+          <t>0,0; 22,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,52</t>
+          <t>0,0; 9,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 10,27</t>
+          <t>1,76; 10,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 19,44</t>
+          <t>5,08; 19,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 15,76</t>
+          <t>1,83; 16,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,91</t>
+          <t>0,47; 4,76</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>8,9%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>17,86%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>11,69%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 13,85</t>
+          <t>6,49; 15,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,97; 23,27</t>
+          <t>8,82; 18,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,5; 16,22</t>
+          <t>8,73; 18,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 14,23</t>
+          <t>2,82; 9,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 14,56</t>
+          <t>5,51; 13,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,09; 18,69</t>
+          <t>12,88; 23,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 19,4</t>
+          <t>7,52; 16,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 9,09</t>
+          <t>5,36; 12,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 12,76</t>
+          <t>6,83; 12,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,03; 19,24</t>
+          <t>12,25; 19,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,13; 16,05</t>
+          <t>9,44; 16,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 10,02</t>
+          <t>4,6; 9,34</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4865</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4616</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1756</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>6520</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>5359</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3328</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4865</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4616</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3473</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>520; 4633</t>
+          <t>1313; 7765</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3642; 11178</t>
+          <t>1945; 9320</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2731; 9599</t>
+          <t>2020; 8270</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1311; 6280</t>
+          <t>0; 2270</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1299; 7635</t>
+          <t>508; 4663</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1980; 8999</t>
+          <t>3290; 10785</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2066; 8618</t>
+          <t>2706; 9119</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2701</t>
+          <t>1183; 5955</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2390; 9478</t>
+          <t>2584; 9607</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6721; 16673</t>
+          <t>6914; 17240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6214; 15128</t>
+          <t>6171; 15299</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1513; 7917</t>
+          <t>1360; 6887</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7127</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11055</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5367</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4978</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6118</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10538</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6217</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7263</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7127</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11055</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5367</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>9148</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2813; 10531</t>
+          <t>3800; 11579</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6349; 16489</t>
+          <t>6422; 16724</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3082; 10527</t>
+          <t>2597; 10527</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3165; 15924</t>
+          <t>2334; 9293</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3765; 11775</t>
+          <t>3220; 10496</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6392; 17100</t>
+          <t>6192; 16578</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2645; 10413</t>
+          <t>3575; 11375</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2695; 10728</t>
+          <t>1998; 7504</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8520; 19278</t>
+          <t>8321; 19853</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15019; 29636</t>
+          <t>14959; 29695</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7338; 17779</t>
+          <t>6890; 16670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8038; 22509</t>
+          <t>5607; 14677</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2751</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4561</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3009</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1296</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5039</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1745</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3152</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2751</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4561</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6280</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3931</t>
+          <t>687; 5654</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2266; 9738</t>
+          <t>848; 7552</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>551; 4779</t>
+          <t>2118; 8827</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1127; 7040</t>
+          <t>866; 7762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>694; 6264</t>
+          <t>0; 3973</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>858; 7143</t>
+          <t>2084; 8929</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1715; 8995</t>
+          <t>550; 4769</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>841; 8152</t>
+          <t>1193; 7133</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1413; 7794</t>
+          <t>1424; 8677</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4515; 13942</t>
+          <t>4489; 13857</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3202; 10964</t>
+          <t>2979; 11058</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2813; 11746</t>
+          <t>2637; 11648</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1985</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4278</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1574</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1272</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1514</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1945</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>612; 5146</t>
+          <t>0; 4527</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1971; 8245</t>
+          <t>0; 3989</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4778</t>
+          <t>0; 4601</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4796</t>
+          <t>0; 3760</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4275</t>
+          <t>608; 5875</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4516</t>
+          <t>1989; 8297</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5120</t>
+          <t>0; 4905</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3572</t>
+          <t>0; 4652</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1249; 7185</t>
+          <t>1231; 7419</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2731; 10116</t>
+          <t>2643; 10262</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>765; 7066</t>
+          <t>822; 7548</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>510; 5578</t>
+          <t>529; 5344</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20465</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16058</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8935</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>11155</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>26375</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>14895</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>15013</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>14682</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20465</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>16058</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>20846</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6600; 17356</t>
+          <t>9344; 21724</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19150; 34373</t>
+          <t>13930; 28618</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9561; 20678</t>
+          <t>10764; 23141</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7984; 25286</t>
+          <t>4658; 15696</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9481; 20949</t>
+          <t>6900; 17203</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14362; 29524</t>
+          <t>19018; 35328</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10447; 23916</t>
+          <t>9591; 21149</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5454; 16563</t>
+          <t>7662; 18239</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17591; 34355</t>
+          <t>18380; 33703</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36772; 58807</t>
+          <t>37446; 58597</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22883; 40249</t>
+          <t>23666; 40267</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16231; 36075</t>
+          <t>14164; 28753</t>
         </is>
       </c>
     </row>
